--- a/src/Excelsior.Tests/LinkTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/LinkTests.Test.verified.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
   </sheets>
 </workbook>
 </file>
@@ -44,12 +44,12 @@
     </border>
   </borders>
   <cellXfs count="4">
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" applyFont="1" applyFill="0" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -57,14 +57,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -204,9 +204,9 @@
   </sheetData>
   <autoFilter ref="A1:C2"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="DeterministicId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="DeterministicId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="DeterministicId3"/>
+    <hyperlink ref="B2" r:id="DeterministicId2"/>
+    <hyperlink ref="C2" r:id="DeterministicId1"/>
+    <hyperlink ref="E2" r:id="DeterministicId3"/>
   </hyperlinks>
 </worksheet>
 </file>
--- a/src/Excelsior.Tests/LinkTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/LinkTests.Test.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -209,4 +209,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="DeterministicId3"/>
   </hyperlinks>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Name"/>
+    <column index="2" property="Link"/>
+    <column index="3" property="NullableLink"/>
+    <column index="4" property="Links"/>
+    <column index="5" property="NullableLinks"/>
+    <column index="6" property="LinksWithNulls"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/LinkTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/LinkTests.Test.verified.xlsx
@@ -61,7 +61,7 @@
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="50" customWidth="1"/>
